--- a/Data/Glados/glados.xlsx
+++ b/Data/Glados/glados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Glados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\SANER2026\Data\Glados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A532F3D-2E51-41AE-A682-77B01566881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C61374-3899-49B9-8016-E407B0239157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
@@ -984,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D38" si="0">E2+F2</f>
+        <f>E2+F2</f>
         <v>331</v>
       </c>
       <c r="E2">
@@ -1027,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:D38" si="0">E3+F3</f>
         <v>331</v>
       </c>
       <c r="E3">

--- a/Data/Glados/glados.xlsx
+++ b/Data/Glados/glados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\SANER2026\Data\Glados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\SANER2027\Data\Glados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C61374-3899-49B9-8016-E407B0239157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1B2B93-F91C-4DA0-B7E2-FB03965E34CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
